--- a/RASTROS_UNODC_Master_DB.xlsx
+++ b/RASTROS_UNODC_Master_DB.xlsx
@@ -14,6 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Respuestas_Formulario_Diagnostico" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mesas_de_Trabajo_y_Capacitaciones" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapeo_Formato_VETTING_Oficial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes_UNODC" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruta_Critica" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuracion_Dashboard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadatos_Proyecto" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -203,6 +207,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -781,42 +791,481 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Pendientes_UNODC — pendientes abiertos; los marcados Resuelto salen del panel.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>FUENTES</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Ruta_Critica — hitos del proyecto, en el orden en que aparecen aquí.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Metas y objetivos: One Pager RASTROS (UNODC).</t>
+          <t>Configuracion_Dashboard — cuota, metas y umbrales de alerta del panel.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Metadatos_Proyecto — títulos y textos del encabezado del panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Metas y objetivos: One Pager RASTROS (UNODC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>67 preguntas: Formulario RASTROS_final_Jalisco.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>31 columnas de vetting: Formato VETTING 2026.xlsx, pestaña Participants.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Fechas y acuerdos logísticos: minuta de la reunión con UNODC del 22/07/2026.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>CUOTA_POR_DEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Propuestas mínimas esperadas por dependencia</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>META_DIAGNOSTICO</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Cuestionarios de diagnóstico previstos en Jalisco</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>FECHA_LIMITE_VETTING</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Fecha límite de envío de propuestas de vetting</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>DIAS_CRITICOS</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Días restantes para considerar la alerta como crítica</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>DIAS_ATENCION</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Días restantes para considerar la alerta como de atención</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$J$2:$J$5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Titulo_Proyecto</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>RASTROS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Subtitulo</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Panel ejecutivo del Enlace Coordinador · Coordinación General Estratégica de Seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Fase_Actual</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Convocatoria de vetting y diagnóstico inicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Julio – Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Paises</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>México (Jalisco) · Guatemala · Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Donante</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Departamento de Estado de EE. UU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Institucion_Ejecutora</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Institucion_Contraparte</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Gobierno del Estado de Jalisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -829,15 +1278,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -868,7 +1323,37 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Estatus_Pendiente</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Nivel_Alerta</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Estatus_Hito</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Tipo_Parametro</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
           <t>Dependencia</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Dependencia_Abrev</t>
         </is>
       </c>
     </row>
@@ -900,7 +1385,37 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
           <t>Coordinación General Estratégica de Seguridad (CGES)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>CGES</t>
         </is>
       </c>
     </row>
@@ -932,7 +1447,37 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>En Gestión</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>En Curso</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
           <t>Secretaría de Seguridad del Estado de Jalisco</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Secretaría de Seguridad</t>
         </is>
       </c>
     </row>
@@ -954,7 +1499,37 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>Secretaría de Seguridad</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Resuelto</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
           <t>Fiscalía del Estado de Jalisco</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Fiscalía del Estado</t>
         </is>
       </c>
     </row>
@@ -971,13 +1546,38 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
+          <t>Fiscalía del Estado</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Booleano</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
           <t>Fiscalía Especializada en Trata de Personas</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Fiscalía Especializada</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>Fiscalía Especializada</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Ministerio Público</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
           <t>Ministerio Público</t>
         </is>
       </c>
@@ -988,30 +1588,70 @@
           <t>Policía Cibernética</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Policía Cibernética</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Policía Cibernética</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="F8" s="5" t="inlineStr">
         <is>
+          <t>Embajada de EE. UU.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
           <t>Perito o personal experto técnico</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Peritos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="F9" s="5" t="inlineStr">
         <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
           <t>Comisión Ejecutiva Estatal de Atención a Víctimas</t>
         </is>
       </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>CEEAV</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="F10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Comisión de Búsqueda de Personas</t>
         </is>
       </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Comisión de Búsqueda</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="F11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Otra</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Otra</t>
         </is>
@@ -4917,7 +5557,7 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Listas_Catalogos!$F$2:$F$11</formula1>
+      <formula1>Listas_Catalogos!$K$2:$K$11</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>Listas_Catalogos!$A$2:$A$3</formula1>
@@ -7930,4 +8570,1365 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID_Pendiente</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Titulo</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Estatus</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Nivel_Alerta</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Fecha_Vencimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Anexo 3</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Confirmar si la Embajada lo requerirá, para anticiparlo en la planeación logística de los oficios.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="n"/>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>P002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Sede de las mesas de trabajo</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>UNODC cubre alquiler, alimentos y coffee break. Falta definir el lugar.</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>En Gestión</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>P003</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Proyección y pantalla</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Por confirmar con la sede una vez definida.</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>P004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Reporte institucional de la capacitación</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Se gestiona internamente; UNODC apoya con los insumos que se requieran.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>En Gestión</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="D2:D61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$F$2:$F$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$G$2:$G$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$H$2:$H$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ID_Hito</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Actividad</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Estatus</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>H001</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>29 de julio de 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Solicitud de vetting al personal de las unidades participantes</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>En Curso</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Fecha límite acordada con UNODC el 22/07/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>H002</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>29 de julio de 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Revisión del formulario de diagnóstico por tomadores de decisiones</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>En Curso</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Solo tomadores de decisiones, para acotar las observaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>H003</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>31 de julio de 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Confirmación de fecha y horario de la reunión presencial</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>CGES</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>H004</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Semana del 24 de agosto de 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Reunión presencial con personal clave y mesas de trabajo</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Sede externa, alimentos y catering a cargo de UNODC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>H005</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Septiembre de 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Aplicación en línea del formulario a todas las unidades</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>UNODC</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Futuro</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$F$2:$F$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas_Catalogos!$I$2:$I$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>